--- a/artfynd/A 14950-2026 artfynd.xlsx
+++ b/artfynd/A 14950-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132911008</v>
+        <v>132911650</v>
       </c>
       <c r="B2" t="n">
-        <v>99140</v>
+        <v>96629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norra Svedsmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546702</v>
+        <v>546618</v>
       </c>
       <c r="R2" t="n">
-        <v>6424526</v>
+        <v>6424522</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,53 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132909974</v>
+        <v>133275166</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>96501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Svedsmossen, Ög</t>
+          <t>Norra svedsmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546712</v>
+        <v>546769</v>
       </c>
       <c r="R3" t="n">
-        <v>6424615</v>
+        <v>6424669</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,28 +855,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132911650</v>
+        <v>133275219</v>
       </c>
       <c r="B4" t="n">
-        <v>96574</v>
+        <v>96410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +885,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norra Svedsmossen, Ög</t>
+          <t>Norra svedsmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546618</v>
+        <v>546721</v>
       </c>
       <c r="R4" t="n">
-        <v>6424522</v>
+        <v>6424609</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,12 +943,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -965,72 +957,67 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132909461</v>
+        <v>133275385</v>
       </c>
       <c r="B5" t="n">
-        <v>99140</v>
+        <v>91995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norra Svedsmossen, Ög</t>
+          <t>Norra svedsmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546633</v>
+        <v>546625</v>
       </c>
       <c r="R5" t="n">
-        <v>6424655</v>
+        <v>6424501</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,12 +1044,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,28 +1058,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132911337</v>
+        <v>132909974</v>
       </c>
       <c r="B6" t="n">
-        <v>56887</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1088,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208255</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norra Svedsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546635</v>
+        <v>546712</v>
       </c>
       <c r="R6" t="n">
-        <v>6424530</v>
+        <v>6424615</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,10 +1182,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133275362</v>
+        <v>133269547</v>
       </c>
       <c r="B7" t="n">
-        <v>106306</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,41 +1193,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norra svedsmossen, Ög</t>
+          <t>Norra Svedsmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546599</v>
+        <v>546600</v>
       </c>
       <c r="R7" t="n">
-        <v>6424625</v>
+        <v>6424613</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,40 +1262,49 @@
           <t>2026-05-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133278375</v>
+        <v>133269554</v>
       </c>
       <c r="B8" t="n">
-        <v>106306</v>
+        <v>58349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1299,37 +1312,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norra Svedsmossen, Norra Svedsmossen, Ög</t>
+          <t>Norra Svedsmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546598</v>
+        <v>546600</v>
       </c>
       <c r="R8" t="n">
-        <v>6424621</v>
+        <v>6424613</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1358,7 +1383,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1368,7 +1393,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1383,22 +1408,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133275234</v>
+        <v>133269555</v>
       </c>
       <c r="B9" t="n">
-        <v>101386</v>
+        <v>58461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1406,41 +1431,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>103018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norra svedsmossen, Ög</t>
+          <t>Norra Svedsmossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546710</v>
+        <v>546600</v>
       </c>
       <c r="R9" t="n">
-        <v>6424597</v>
+        <v>6424613</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,57 +1500,66 @@
           <t>2026-05-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Alessandra Munari</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133269547</v>
+        <v>133269556</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>58658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1534,7 +1576,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1579,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1589,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133275251</v>
+        <v>132911337</v>
       </c>
       <c r="B11" t="n">
-        <v>101386</v>
+        <v>56904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1627,38 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>208255</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norra svedsmossen, Ög</t>
+          <t>Norra Svedsmossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546691</v>
+        <v>546635</v>
       </c>
       <c r="R11" t="n">
-        <v>6424626</v>
+        <v>6424530</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,12 +1723,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1699,65 +1737,64 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133269554</v>
+        <v>132909398</v>
       </c>
       <c r="B12" t="n">
-        <v>58349</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1765,13 +1802,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546600</v>
+        <v>546633</v>
       </c>
       <c r="R12" t="n">
-        <v>6424613</v>
+        <v>6424655</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,22 +1832,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1819,28 +1846,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133275352</v>
+        <v>132911008</v>
       </c>
       <c r="B13" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,23 +1895,24 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norra svedsmossen, Ög</t>
+          <t>Norra Svedsmossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546596</v>
+        <v>546702</v>
       </c>
       <c r="R13" t="n">
-        <v>6424627</v>
+        <v>6424526</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1910,12 +1939,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,56 +1953,60 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133275385</v>
+        <v>133275284</v>
       </c>
       <c r="B14" t="n">
-        <v>91978</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1981,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546625</v>
+        <v>546609</v>
       </c>
       <c r="R14" t="n">
-        <v>6424501</v>
+        <v>6424650</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,35 +2077,39 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133275202</v>
+        <v>133275352</v>
       </c>
       <c r="B15" t="n">
-        <v>101386</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -2083,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546738</v>
+        <v>546596</v>
       </c>
       <c r="R15" t="n">
-        <v>6424655</v>
+        <v>6424627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,60 +2183,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133269556</v>
+        <v>133275378</v>
       </c>
       <c r="B16" t="n">
-        <v>58658</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norra Svedsmossen, Ög</t>
+          <t>Norra svedsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546600</v>
+        <v>546616</v>
       </c>
       <c r="R16" t="n">
-        <v>6424613</v>
+        <v>6424525</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2226,86 +2259,77 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133269555</v>
+        <v>133269558</v>
       </c>
       <c r="B17" t="n">
-        <v>58461</v>
+        <v>106324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103018</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norra Svedsmossen, Ög</t>
@@ -2347,7 +2371,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2357,7 +2381,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2384,39 +2408,35 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133275378</v>
+        <v>133275362</v>
       </c>
       <c r="B18" t="n">
-        <v>99178</v>
+        <v>106324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -2427,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546616</v>
+        <v>546599</v>
       </c>
       <c r="R18" t="n">
-        <v>6424525</v>
+        <v>6424625</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,10 +2510,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133278464</v>
+        <v>133278375</v>
       </c>
       <c r="B19" t="n">
-        <v>106306</v>
+        <v>106324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546587</v>
+        <v>546598</v>
       </c>
       <c r="R19" t="n">
-        <v>6424622</v>
+        <v>6424621</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2597,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133278901</v>
+        <v>133278464</v>
       </c>
       <c r="B20" t="n">
-        <v>102301</v>
+        <v>106324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2608,21 +2628,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2632,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546663</v>
+        <v>546587</v>
       </c>
       <c r="R20" t="n">
-        <v>6424715</v>
+        <v>6424622</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,7 +2687,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2677,7 +2697,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,60 +2724,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133269558</v>
+        <v>133278901</v>
       </c>
       <c r="B21" t="n">
-        <v>106306</v>
+        <v>102318</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>221235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norra Svedsmossen, Ög</t>
+          <t>Norra Svedsmossen, Norra Svedsmossen, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546600</v>
+        <v>546663</v>
       </c>
       <c r="R21" t="n">
-        <v>6424613</v>
+        <v>6424715</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2786,7 +2794,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2796,7 +2804,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2811,22 +2819,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133275166</v>
+        <v>133275202</v>
       </c>
       <c r="B22" t="n">
-        <v>96484</v>
+        <v>101403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,21 +2842,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2862,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546769</v>
+        <v>546738</v>
       </c>
       <c r="R22" t="n">
-        <v>6424669</v>
+        <v>6424655</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,39 +2933,35 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133275284</v>
+        <v>133275234</v>
       </c>
       <c r="B23" t="n">
-        <v>99178</v>
+        <v>101403</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -2968,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546609</v>
+        <v>546710</v>
       </c>
       <c r="R23" t="n">
-        <v>6424650</v>
+        <v>6424597</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3028,6 +3032,108 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133275251</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norra svedsmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>546691</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6424626</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14950-2026 artfynd.xlsx
+++ b/artfynd/A 14950-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132911650</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275166</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275219</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275385</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132909974</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133269547</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133269554</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133269555</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133269556</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132911337</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1862,6 +1917,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132909398</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132911008</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2074,6 +2139,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275284</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2180,6 +2250,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275352</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2286,6 +2361,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275378</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2405,6 +2485,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133269558</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2507,6 +2592,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275362</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2614,6 +2704,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133278375</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2721,6 +2816,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133278464</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2828,6 +2928,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133278901</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2930,6 +3035,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275202</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3032,6 +3142,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275234</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3134,8 +3249,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275251</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>